--- a/Integrated Exam Management Information System/IEMIS Upload File.xlsx
+++ b/Integrated Exam Management Information System/IEMIS Upload File.xlsx
@@ -1283,29 +1283,8 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1317,6 +1296,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="13" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1331,6 +1319,15 @@
     <xf numFmtId="49" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="49" fontId="15" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1340,8 +1337,11 @@
     <xf numFmtId="49" fontId="4" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1449,16 +1449,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>501650</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>107950</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>482600</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>120650</xdr:rowOff>
+      <xdr:colOff>279400</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1467,8 +1467,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="6553200" y="7893050"/>
-          <a:ext cx="2997200" cy="4616450"/>
+          <a:off x="7562850" y="7918450"/>
+          <a:ext cx="1784350" cy="4406900"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1478,14 +1478,14 @@
         </a:ln>
       </xdr:spPr>
       <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
+        <a:lnRef idx="3">
+          <a:schemeClr val="accent2"/>
         </a:lnRef>
         <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
+          <a:schemeClr val="accent2"/>
         </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent2"/>
         </a:effectRef>
         <a:fontRef idx="minor">
           <a:schemeClr val="tx1"/>
@@ -1496,16 +1496,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>387350</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:rowOff>69850</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>50800</xdr:colOff>
+      <xdr:colOff>101600</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>2952750</xdr:rowOff>
+      <xdr:rowOff>1390650</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1514,8 +1514,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="3695700" y="8477250"/>
-          <a:ext cx="2406650" cy="2895600"/>
+          <a:off x="4743450" y="8489950"/>
+          <a:ext cx="1409700" cy="1320800"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1525,14 +1525,108 @@
         </a:ln>
       </xdr:spPr>
       <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2"/>
         </a:lnRef>
         <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
+          <a:schemeClr val="accent2"/>
         </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>241300</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>203200</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>2984500</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="9" name="Straight Arrow Connector 8"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="4432300" y="8515350"/>
+          <a:ext cx="4838700" cy="2889250"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>2000250</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="19" name="Straight Arrow Connector 18"/>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="4826000" y="8521700"/>
+          <a:ext cx="2717800" cy="1898650"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent2"/>
         </a:effectRef>
         <a:fontRef idx="minor">
           <a:schemeClr val="tx1"/>
@@ -2965,104 +3059,104 @@
       <c r="N2" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="O2" s="137" t="s">
+      <c r="O2" s="133" t="s">
         <v>120</v>
       </c>
-      <c r="P2" s="138"/>
-      <c r="Q2" s="138"/>
-      <c r="R2" s="138"/>
-      <c r="S2" s="139"/>
-      <c r="T2" s="137" t="s">
+      <c r="P2" s="134"/>
+      <c r="Q2" s="134"/>
+      <c r="R2" s="134"/>
+      <c r="S2" s="135"/>
+      <c r="T2" s="133" t="s">
         <v>122</v>
       </c>
-      <c r="U2" s="138"/>
-      <c r="V2" s="138"/>
-      <c r="W2" s="138"/>
-      <c r="X2" s="139"/>
-      <c r="Y2" s="140" t="s">
+      <c r="U2" s="134"/>
+      <c r="V2" s="134"/>
+      <c r="W2" s="134"/>
+      <c r="X2" s="135"/>
+      <c r="Y2" s="136" t="s">
         <v>123</v>
       </c>
-      <c r="Z2" s="131"/>
-      <c r="AA2" s="131"/>
-      <c r="AB2" s="131"/>
-      <c r="AC2" s="132"/>
-      <c r="AD2" s="130" t="s">
+      <c r="Z2" s="137"/>
+      <c r="AA2" s="137"/>
+      <c r="AB2" s="137"/>
+      <c r="AC2" s="138"/>
+      <c r="AD2" s="139" t="s">
         <v>121</v>
       </c>
-      <c r="AE2" s="131"/>
-      <c r="AF2" s="131"/>
-      <c r="AG2" s="131"/>
-      <c r="AH2" s="132"/>
-      <c r="AI2" s="141" t="s">
+      <c r="AE2" s="137"/>
+      <c r="AF2" s="137"/>
+      <c r="AG2" s="137"/>
+      <c r="AH2" s="138"/>
+      <c r="AI2" s="140" t="s">
         <v>129</v>
       </c>
-      <c r="AJ2" s="142"/>
-      <c r="AK2" s="142"/>
-      <c r="AL2" s="142"/>
-      <c r="AM2" s="143"/>
-      <c r="AN2" s="141" t="s">
+      <c r="AJ2" s="141"/>
+      <c r="AK2" s="141"/>
+      <c r="AL2" s="141"/>
+      <c r="AM2" s="142"/>
+      <c r="AN2" s="140" t="s">
         <v>130</v>
       </c>
-      <c r="AO2" s="142"/>
-      <c r="AP2" s="142"/>
-      <c r="AQ2" s="142"/>
-      <c r="AR2" s="143"/>
-      <c r="AS2" s="134" t="s">
+      <c r="AO2" s="141"/>
+      <c r="AP2" s="141"/>
+      <c r="AQ2" s="141"/>
+      <c r="AR2" s="142"/>
+      <c r="AS2" s="127" t="s">
         <v>132</v>
       </c>
-      <c r="AT2" s="135"/>
-      <c r="AU2" s="135"/>
-      <c r="AV2" s="135"/>
-      <c r="AW2" s="136"/>
-      <c r="AX2" s="134" t="s">
+      <c r="AT2" s="128"/>
+      <c r="AU2" s="128"/>
+      <c r="AV2" s="128"/>
+      <c r="AW2" s="129"/>
+      <c r="AX2" s="127" t="s">
         <v>131</v>
       </c>
-      <c r="AY2" s="135"/>
-      <c r="AZ2" s="135"/>
-      <c r="BA2" s="135"/>
-      <c r="BB2" s="136"/>
-      <c r="BC2" s="125" t="s">
+      <c r="AY2" s="128"/>
+      <c r="AZ2" s="128"/>
+      <c r="BA2" s="128"/>
+      <c r="BB2" s="129"/>
+      <c r="BC2" s="130" t="s">
         <v>133</v>
       </c>
-      <c r="BD2" s="126"/>
-      <c r="BE2" s="126"/>
-      <c r="BF2" s="126"/>
-      <c r="BG2" s="127"/>
-      <c r="BH2" s="125" t="s">
+      <c r="BD2" s="131"/>
+      <c r="BE2" s="131"/>
+      <c r="BF2" s="131"/>
+      <c r="BG2" s="132"/>
+      <c r="BH2" s="130" t="s">
         <v>134</v>
       </c>
-      <c r="BI2" s="126"/>
-      <c r="BJ2" s="126"/>
-      <c r="BK2" s="126"/>
-      <c r="BL2" s="127"/>
-      <c r="BM2" s="130" t="s">
+      <c r="BI2" s="131"/>
+      <c r="BJ2" s="131"/>
+      <c r="BK2" s="131"/>
+      <c r="BL2" s="132"/>
+      <c r="BM2" s="139" t="s">
         <v>135</v>
       </c>
-      <c r="BN2" s="131"/>
-      <c r="BO2" s="131"/>
-      <c r="BP2" s="131"/>
-      <c r="BQ2" s="132"/>
-      <c r="BR2" s="130" t="s">
+      <c r="BN2" s="137"/>
+      <c r="BO2" s="137"/>
+      <c r="BP2" s="137"/>
+      <c r="BQ2" s="138"/>
+      <c r="BR2" s="139" t="s">
         <v>136</v>
       </c>
-      <c r="BS2" s="131"/>
-      <c r="BT2" s="131"/>
-      <c r="BU2" s="131"/>
-      <c r="BV2" s="132"/>
-      <c r="BW2" s="125" t="s">
+      <c r="BS2" s="137"/>
+      <c r="BT2" s="137"/>
+      <c r="BU2" s="137"/>
+      <c r="BV2" s="138"/>
+      <c r="BW2" s="130" t="s">
         <v>137</v>
       </c>
-      <c r="BX2" s="126"/>
-      <c r="BY2" s="126"/>
-      <c r="BZ2" s="126"/>
-      <c r="CA2" s="127"/>
-      <c r="CB2" s="125" t="s">
+      <c r="BX2" s="131"/>
+      <c r="BY2" s="131"/>
+      <c r="BZ2" s="131"/>
+      <c r="CA2" s="132"/>
+      <c r="CB2" s="130" t="s">
         <v>138</v>
       </c>
-      <c r="CC2" s="126"/>
-      <c r="CD2" s="126"/>
-      <c r="CE2" s="126"/>
-      <c r="CF2" s="127"/>
+      <c r="CC2" s="131"/>
+      <c r="CD2" s="131"/>
+      <c r="CE2" s="131"/>
+      <c r="CF2" s="132"/>
       <c r="CG2" s="57" t="s">
         <v>50</v>
       </c>
@@ -21188,20 +21282,20 @@
         <v>171</v>
       </c>
       <c r="J31" s="74"/>
-      <c r="K31" s="128" t="s">
+      <c r="K31" s="143" t="s">
         <v>181</v>
       </c>
-      <c r="L31" s="129"/>
-      <c r="M31" s="129"/>
-      <c r="N31" s="129"/>
-      <c r="O31" s="129"/>
-      <c r="P31" s="128" t="s">
+      <c r="L31" s="144"/>
+      <c r="M31" s="144"/>
+      <c r="N31" s="144"/>
+      <c r="O31" s="144"/>
+      <c r="P31" s="143" t="s">
         <v>182</v>
       </c>
-      <c r="Q31" s="128"/>
-      <c r="R31" s="128"/>
-      <c r="S31" s="128"/>
-      <c r="T31" s="128"/>
+      <c r="Q31" s="143"/>
+      <c r="R31" s="143"/>
+      <c r="S31" s="143"/>
+      <c r="T31" s="143"/>
       <c r="X31" s="38"/>
       <c r="AM31" s="38"/>
       <c r="AQ31" s="30"/>
@@ -21266,10 +21360,10 @@
         <v>8</v>
       </c>
       <c r="D33" s="38"/>
-      <c r="E33" s="133" t="s">
+      <c r="E33" s="126" t="s">
         <v>10</v>
       </c>
-      <c r="F33" s="133"/>
+      <c r="F33" s="126"/>
       <c r="J33" s="76" t="s">
         <v>184</v>
       </c>
@@ -21730,15 +21824,15 @@
       <c r="A53" s="40"/>
       <c r="B53" s="40"/>
       <c r="D53" s="38"/>
-      <c r="J53" s="144" t="s">
+      <c r="J53" s="125" t="s">
         <v>200</v>
       </c>
-      <c r="K53" s="144"/>
-      <c r="L53" s="144"/>
-      <c r="M53" s="144"/>
-      <c r="N53" s="144"/>
-      <c r="O53" s="144"/>
-      <c r="P53" s="144"/>
+      <c r="K53" s="125"/>
+      <c r="L53" s="125"/>
+      <c r="M53" s="125"/>
+      <c r="N53" s="125"/>
+      <c r="O53" s="125"/>
+      <c r="P53" s="125"/>
       <c r="X53" s="38"/>
       <c r="AM53" s="38"/>
       <c r="AQ53" s="30"/>
@@ -29894,6 +29988,12 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="BW2:CA2"/>
+    <mergeCell ref="CB2:CF2"/>
+    <mergeCell ref="K31:O31"/>
+    <mergeCell ref="P31:T31"/>
+    <mergeCell ref="BM2:BQ2"/>
+    <mergeCell ref="BR2:BV2"/>
     <mergeCell ref="E33:F33"/>
     <mergeCell ref="AS2:AW2"/>
     <mergeCell ref="AX2:BB2"/>
@@ -29905,12 +30005,6 @@
     <mergeCell ref="AD2:AH2"/>
     <mergeCell ref="AI2:AM2"/>
     <mergeCell ref="AN2:AR2"/>
-    <mergeCell ref="BW2:CA2"/>
-    <mergeCell ref="CB2:CF2"/>
-    <mergeCell ref="K31:O31"/>
-    <mergeCell ref="P31:T31"/>
-    <mergeCell ref="BM2:BQ2"/>
-    <mergeCell ref="BR2:BV2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" prompt="Enter a value that satisfies the formula: =COUNTIFS($D$2:$D$107,D2)&lt;=1" sqref="L9">
@@ -31148,104 +31242,104 @@
       <c r="N2" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="O2" s="137" t="s">
+      <c r="O2" s="133" t="s">
         <v>120</v>
       </c>
-      <c r="P2" s="138"/>
-      <c r="Q2" s="138"/>
-      <c r="R2" s="138"/>
-      <c r="S2" s="139"/>
-      <c r="T2" s="137" t="s">
+      <c r="P2" s="134"/>
+      <c r="Q2" s="134"/>
+      <c r="R2" s="134"/>
+      <c r="S2" s="135"/>
+      <c r="T2" s="133" t="s">
         <v>122</v>
       </c>
-      <c r="U2" s="138"/>
-      <c r="V2" s="138"/>
-      <c r="W2" s="138"/>
-      <c r="X2" s="139"/>
-      <c r="Y2" s="140" t="s">
+      <c r="U2" s="134"/>
+      <c r="V2" s="134"/>
+      <c r="W2" s="134"/>
+      <c r="X2" s="135"/>
+      <c r="Y2" s="136" t="s">
         <v>123</v>
       </c>
-      <c r="Z2" s="131"/>
-      <c r="AA2" s="131"/>
-      <c r="AB2" s="131"/>
-      <c r="AC2" s="132"/>
-      <c r="AD2" s="130" t="s">
+      <c r="Z2" s="137"/>
+      <c r="AA2" s="137"/>
+      <c r="AB2" s="137"/>
+      <c r="AC2" s="138"/>
+      <c r="AD2" s="139" t="s">
         <v>121</v>
       </c>
-      <c r="AE2" s="131"/>
-      <c r="AF2" s="131"/>
-      <c r="AG2" s="131"/>
-      <c r="AH2" s="132"/>
-      <c r="AI2" s="141" t="s">
+      <c r="AE2" s="137"/>
+      <c r="AF2" s="137"/>
+      <c r="AG2" s="137"/>
+      <c r="AH2" s="138"/>
+      <c r="AI2" s="140" t="s">
         <v>129</v>
       </c>
-      <c r="AJ2" s="142"/>
-      <c r="AK2" s="142"/>
-      <c r="AL2" s="142"/>
-      <c r="AM2" s="143"/>
-      <c r="AN2" s="141" t="s">
+      <c r="AJ2" s="141"/>
+      <c r="AK2" s="141"/>
+      <c r="AL2" s="141"/>
+      <c r="AM2" s="142"/>
+      <c r="AN2" s="140" t="s">
         <v>130</v>
       </c>
-      <c r="AO2" s="142"/>
-      <c r="AP2" s="142"/>
-      <c r="AQ2" s="142"/>
-      <c r="AR2" s="143"/>
-      <c r="AS2" s="134" t="s">
+      <c r="AO2" s="141"/>
+      <c r="AP2" s="141"/>
+      <c r="AQ2" s="141"/>
+      <c r="AR2" s="142"/>
+      <c r="AS2" s="127" t="s">
         <v>132</v>
       </c>
-      <c r="AT2" s="135"/>
-      <c r="AU2" s="135"/>
-      <c r="AV2" s="135"/>
-      <c r="AW2" s="136"/>
-      <c r="AX2" s="134" t="s">
+      <c r="AT2" s="128"/>
+      <c r="AU2" s="128"/>
+      <c r="AV2" s="128"/>
+      <c r="AW2" s="129"/>
+      <c r="AX2" s="127" t="s">
         <v>131</v>
       </c>
-      <c r="AY2" s="135"/>
-      <c r="AZ2" s="135"/>
-      <c r="BA2" s="135"/>
-      <c r="BB2" s="136"/>
-      <c r="BC2" s="125" t="s">
+      <c r="AY2" s="128"/>
+      <c r="AZ2" s="128"/>
+      <c r="BA2" s="128"/>
+      <c r="BB2" s="129"/>
+      <c r="BC2" s="130" t="s">
         <v>133</v>
       </c>
-      <c r="BD2" s="126"/>
-      <c r="BE2" s="126"/>
-      <c r="BF2" s="126"/>
-      <c r="BG2" s="127"/>
-      <c r="BH2" s="125" t="s">
+      <c r="BD2" s="131"/>
+      <c r="BE2" s="131"/>
+      <c r="BF2" s="131"/>
+      <c r="BG2" s="132"/>
+      <c r="BH2" s="130" t="s">
         <v>134</v>
       </c>
-      <c r="BI2" s="126"/>
-      <c r="BJ2" s="126"/>
-      <c r="BK2" s="126"/>
-      <c r="BL2" s="127"/>
-      <c r="BM2" s="130" t="s">
+      <c r="BI2" s="131"/>
+      <c r="BJ2" s="131"/>
+      <c r="BK2" s="131"/>
+      <c r="BL2" s="132"/>
+      <c r="BM2" s="139" t="s">
         <v>135</v>
       </c>
-      <c r="BN2" s="131"/>
-      <c r="BO2" s="131"/>
-      <c r="BP2" s="131"/>
-      <c r="BQ2" s="132"/>
-      <c r="BR2" s="130" t="s">
+      <c r="BN2" s="137"/>
+      <c r="BO2" s="137"/>
+      <c r="BP2" s="137"/>
+      <c r="BQ2" s="138"/>
+      <c r="BR2" s="139" t="s">
         <v>136</v>
       </c>
-      <c r="BS2" s="131"/>
-      <c r="BT2" s="131"/>
-      <c r="BU2" s="131"/>
-      <c r="BV2" s="132"/>
-      <c r="BW2" s="125" t="s">
+      <c r="BS2" s="137"/>
+      <c r="BT2" s="137"/>
+      <c r="BU2" s="137"/>
+      <c r="BV2" s="138"/>
+      <c r="BW2" s="130" t="s">
         <v>137</v>
       </c>
-      <c r="BX2" s="126"/>
-      <c r="BY2" s="126"/>
-      <c r="BZ2" s="126"/>
-      <c r="CA2" s="127"/>
-      <c r="CB2" s="125" t="s">
+      <c r="BX2" s="131"/>
+      <c r="BY2" s="131"/>
+      <c r="BZ2" s="131"/>
+      <c r="CA2" s="132"/>
+      <c r="CB2" s="130" t="s">
         <v>138</v>
       </c>
-      <c r="CC2" s="126"/>
-      <c r="CD2" s="126"/>
-      <c r="CE2" s="126"/>
-      <c r="CF2" s="127"/>
+      <c r="CC2" s="131"/>
+      <c r="CD2" s="131"/>
+      <c r="CE2" s="131"/>
+      <c r="CF2" s="132"/>
       <c r="CG2" s="57" t="s">
         <v>50</v>
       </c>
@@ -46123,12 +46217,6 @@
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="AN2:AR2"/>
-    <mergeCell ref="O2:S2"/>
-    <mergeCell ref="T2:X2"/>
-    <mergeCell ref="Y2:AC2"/>
-    <mergeCell ref="AD2:AH2"/>
-    <mergeCell ref="AI2:AM2"/>
     <mergeCell ref="BW2:CA2"/>
     <mergeCell ref="CB2:CF2"/>
     <mergeCell ref="AS2:AW2"/>
@@ -46137,6 +46225,12 @@
     <mergeCell ref="BH2:BL2"/>
     <mergeCell ref="BM2:BQ2"/>
     <mergeCell ref="BR2:BV2"/>
+    <mergeCell ref="AN2:AR2"/>
+    <mergeCell ref="O2:S2"/>
+    <mergeCell ref="T2:X2"/>
+    <mergeCell ref="Y2:AC2"/>
+    <mergeCell ref="AD2:AH2"/>
+    <mergeCell ref="AI2:AM2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" prompt="Enter a value that satisfies the formula: =COUNTIFS($D$2:$D$107,D2)&lt;=1" sqref="L9">
